--- a/config/character.xlsx
+++ b/config/character.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>衝動的</t>
+          <t>冲动</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>頑張り屋</t>
+          <t>拼命三郎</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>シャイ</t>
+          <t>害羞</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>せっかち</t>
+          <t>性急</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>爽やか</t>
+          <t>清爽</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>無邪気</t>
+          <t>天真</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>寂しがり屋</t>
+          <t>怕寂寞的人</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>頑固</t>
+          <t>顽固</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>やんちゃ</t>
+          <t>调皮</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>マイペース</t>
+          <t>我行我素</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>おてんば</t>
+          <t>假小子</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>楽天家</t>
+          <t>乐天派</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>のんびり</t>
+          <t>悠闲</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>大雑把</t>
+          <t>粗略</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>優しい</t>
+          <t>温柔</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>従順</t>
+          <t>顺从</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>自信満々</t>
+          <t>自信满满</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
